--- a/lll/Estadística Descriptiva/Practica 1/base_estadistica_descriptiva_100_registros.xlsx
+++ b/lll/Estadística Descriptiva/Practica 1/base_estadistica_descriptiva_100_registros.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Caso Curso Pensamiento\Nuevo Codigo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\IUCMC\lll\Estadística Descriptiva\Practica 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA963D8-F82B-4AC7-B997-C4EB7F4C55D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7890" activeTab="2"/>
+    <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="datos_estudiantes" sheetId="1" r:id="rId1"/>
+    <sheet name="datos" sheetId="1" r:id="rId1"/>
     <sheet name="diccionario" sheetId="2" r:id="rId2"/>
     <sheet name="cargar_en_R" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">datos_estudiantes!$A$3:$I$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">datos!$A$3:$I$103</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -219,7 +220,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -617,9 +618,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I103"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.09765625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -632,7 +633,7 @@
     <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.899999999999999" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" ht="17.3" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -645,7 +646,7 @@
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -658,7 +659,7 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -687,7 +688,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -716,7 +717,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -745,7 +746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -774,7 +775,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -803,7 +804,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -832,7 +833,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -861,7 +862,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -890,7 +891,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -919,7 +920,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -948,7 +949,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -977,7 +978,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -1006,7 +1007,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1035,7 +1036,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -1064,7 +1065,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1093,7 +1094,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -1122,7 +1123,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1151,7 +1152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -1180,7 +1181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1209,7 +1210,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -1238,7 +1239,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1267,7 +1268,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -1296,7 +1297,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>22</v>
       </c>
@@ -1325,7 +1326,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -1354,7 +1355,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>24</v>
       </c>
@@ -1383,7 +1384,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -1412,7 +1413,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26</v>
       </c>
@@ -1441,7 +1442,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -1470,7 +1471,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>28</v>
       </c>
@@ -1499,7 +1500,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -1528,7 +1529,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>30</v>
       </c>
@@ -1557,7 +1558,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -1586,7 +1587,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>32</v>
       </c>
@@ -1615,7 +1616,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>33</v>
       </c>
@@ -1644,7 +1645,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>34</v>
       </c>
@@ -1673,7 +1674,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>35</v>
       </c>
@@ -1702,7 +1703,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>36</v>
       </c>
@@ -1731,7 +1732,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>37</v>
       </c>
@@ -1760,7 +1761,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>38</v>
       </c>
@@ -1789,7 +1790,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>39</v>
       </c>
@@ -1818,7 +1819,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>40</v>
       </c>
@@ -1847,7 +1848,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>41</v>
       </c>
@@ -1876,7 +1877,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>42</v>
       </c>
@@ -1905,7 +1906,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>43</v>
       </c>
@@ -1934,7 +1935,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>44</v>
       </c>
@@ -1963,7 +1964,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>45</v>
       </c>
@@ -1992,7 +1993,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>46</v>
       </c>
@@ -2021,7 +2022,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>47</v>
       </c>
@@ -2050,7 +2051,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>48</v>
       </c>
@@ -2079,7 +2080,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>49</v>
       </c>
@@ -2108,7 +2109,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>50</v>
       </c>
@@ -2137,7 +2138,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>51</v>
       </c>
@@ -2166,7 +2167,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>52</v>
       </c>
@@ -2195,7 +2196,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>53</v>
       </c>
@@ -2224,7 +2225,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>54</v>
       </c>
@@ -2253,7 +2254,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>55</v>
       </c>
@@ -2282,7 +2283,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>56</v>
       </c>
@@ -2311,7 +2312,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>57</v>
       </c>
@@ -2340,7 +2341,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>58</v>
       </c>
@@ -2369,7 +2370,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>59</v>
       </c>
@@ -2398,7 +2399,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>60</v>
       </c>
@@ -2427,7 +2428,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>61</v>
       </c>
@@ -2456,7 +2457,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>62</v>
       </c>
@@ -2485,7 +2486,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>63</v>
       </c>
@@ -2514,7 +2515,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>64</v>
       </c>
@@ -2543,7 +2544,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>65</v>
       </c>
@@ -2572,7 +2573,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>66</v>
       </c>
@@ -2601,7 +2602,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>67</v>
       </c>
@@ -2630,7 +2631,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>68</v>
       </c>
@@ -2659,7 +2660,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>69</v>
       </c>
@@ -2688,7 +2689,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>70</v>
       </c>
@@ -2717,7 +2718,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>71</v>
       </c>
@@ -2746,7 +2747,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>72</v>
       </c>
@@ -2775,7 +2776,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>73</v>
       </c>
@@ -2804,7 +2805,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>74</v>
       </c>
@@ -2833,7 +2834,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>75</v>
       </c>
@@ -2862,7 +2863,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>76</v>
       </c>
@@ -2891,7 +2892,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>77</v>
       </c>
@@ -2920,7 +2921,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>78</v>
       </c>
@@ -2949,7 +2950,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>79</v>
       </c>
@@ -2978,7 +2979,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>80</v>
       </c>
@@ -3007,7 +3008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>81</v>
       </c>
@@ -3036,7 +3037,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>82</v>
       </c>
@@ -3065,7 +3066,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>83</v>
       </c>
@@ -3094,7 +3095,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>84</v>
       </c>
@@ -3123,7 +3124,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>85</v>
       </c>
@@ -3152,7 +3153,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>86</v>
       </c>
@@ -3181,7 +3182,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>87</v>
       </c>
@@ -3210,7 +3211,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>88</v>
       </c>
@@ -3239,7 +3240,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>89</v>
       </c>
@@ -3268,7 +3269,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>90</v>
       </c>
@@ -3297,7 +3298,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>91</v>
       </c>
@@ -3326,7 +3327,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>92</v>
       </c>
@@ -3355,7 +3356,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>93</v>
       </c>
@@ -3384,7 +3385,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>94</v>
       </c>
@@ -3413,7 +3414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>95</v>
       </c>
@@ -3442,7 +3443,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>96</v>
       </c>
@@ -3471,7 +3472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>97</v>
       </c>
@@ -3500,7 +3501,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>98</v>
       </c>
@@ -3529,7 +3530,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>99</v>
       </c>
@@ -3558,7 +3559,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>100</v>
       </c>
@@ -3588,7 +3589,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I103"/>
+  <autoFilter ref="A3:I103" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -3598,9 +3599,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.09765625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -3608,7 +3609,7 @@
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.899999999999999" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="17.3" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>23</v>
       </c>
@@ -3616,7 +3617,7 @@
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>24</v>
       </c>
@@ -3630,7 +3631,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -3644,7 +3645,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3658,7 +3659,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3672,7 +3673,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -3686,7 +3687,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3700,7 +3701,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -3714,7 +3715,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -3728,7 +3729,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3742,7 +3743,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3765,21 +3766,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.09765625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="82" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.899999999999999" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" ht="17.3" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>51</v>
       </c>
       <c r="B1" s="8"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>52</v>
       </c>
@@ -3787,7 +3788,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -3795,7 +3796,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -3803,7 +3804,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -3811,7 +3812,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -3819,7 +3820,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>61</v>
       </c>
